--- a/Data/Excel/world_building.xlsx
+++ b/Data/Excel/world_building.xlsx
@@ -1239,9 +1239,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" ns3:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="19.875" customWidth="1"/>
     <col min="4" max="4" width="24.125" customWidth="1"/>
@@ -1249,260 +1249,422 @@
     <col min="9" max="9" width="42.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T1" t="s">
-        <v>30</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>buildingType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>subType</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sizeX</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sizeZ</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prefabLocation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>iconLocation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>maxCount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>unlockHouseLevel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>unlockBuildingId</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>unlockBuildingLevel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>enable</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>buildCategory</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>sortOrder</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>showInBuildPanel</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>defaultUnlocked</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>unlockSourceType</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" t="s">
-        <v>10</v>
-      </c>
-      <c r="O2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" t="s">
-        <v>10</v>
-      </c>
-      <c r="T2" t="s">
-        <v>8</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" t="s">
-        <v>12</v>
-      </c>
-      <c r="P3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>12</v>
-      </c>
-      <c r="R3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S3" t="s">
-        <v>12</v>
-      </c>
-      <c r="T3" t="s">
-        <v>12</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" t="s">
-        <v>42</v>
-      </c>
-      <c r="T4" t="s">
-        <v>43</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>building id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>building type</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sub type</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>size x</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>size z</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>prefab location</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>max count</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>unlock house level</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unlock building id</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>unlock building level</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>enable</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>build page category</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>build page sort order</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>building description</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>show in build panel</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>default unlocked</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>unlock source type: 0 none, 1 default, 2 tech, 3 runtime</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="B5">
         <v>30000001</v>
       </c>
-      <c r="C5" t="s">
-        <v>44</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>House</t>
+        </is>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1516,11 +1678,15 @@
       <c r="G5">
         <v>3</v>
       </c>
-      <c r="H5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" t="s">
-        <v>80</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Structure/House/House.prefab</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/System/House.png</t>
+        </is>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1543,8 +1709,10 @@
       <c r="P5">
         <v>10</v>
       </c>
-      <c r="Q5" t="s">
-        <v>46</v>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>First home. Unlocks early world building progression.</t>
+        </is>
       </c>
       <c r="R5">
         <v>1</v>
@@ -1556,12 +1724,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="B6">
         <v>30000002</v>
       </c>
-      <c r="C6" t="s">
-        <v>79</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1575,8 +1745,10 @@
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
-        <v>47</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Structure/Storage/Storage.prefab</t>
+        </is>
       </c>
       <c r="J6">
         <v>10</v>
@@ -1599,8 +1771,10 @@
       <c r="P6">
         <v>20</v>
       </c>
-      <c r="Q6" t="s">
-        <v>48</v>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Stores long-term resources.</t>
+        </is>
       </c>
       <c r="R6">
         <v>1</v>
@@ -1612,12 +1786,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="B7">
         <v>30000003</v>
       </c>
-      <c r="C7" t="s">
-        <v>49</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Workbench</t>
+        </is>
       </c>
       <c r="D7">
         <v>3</v>
@@ -1631,8 +1807,10 @@
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
-        <v>50</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Structure/Lab/Lab.prefab</t>
+        </is>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1655,25 +1833,29 @@
       <c r="P7">
         <v>10</v>
       </c>
-      <c r="Q7" t="s">
-        <v>51</v>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Basic crafting and early production.</t>
+        </is>
       </c>
       <c r="R7">
         <v>1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="B8">
         <v>30000004</v>
       </c>
-      <c r="C8" t="s">
-        <v>52</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Carpentry Bench</t>
+        </is>
       </c>
       <c r="D8">
         <v>4</v>
@@ -1687,8 +1869,10 @@
       <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" t="s">
-        <v>53</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Structure/Woodland/Woodland.prefab</t>
+        </is>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1711,8 +1895,10 @@
       <c r="P8">
         <v>20</v>
       </c>
-      <c r="Q8" t="s">
-        <v>54</v>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Processes wood and carpentry recipes.</t>
+        </is>
       </c>
       <c r="R8">
         <v>1</v>
@@ -1724,12 +1910,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="B9">
         <v>30000005</v>
       </c>
-      <c r="C9" t="s">
-        <v>55</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Furnace</t>
+        </is>
       </c>
       <c r="D9">
         <v>5</v>
@@ -1743,8 +1931,10 @@
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>56</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Map/Buildings/Prefabs/WorldFurnace.prefab</t>
+        </is>
       </c>
       <c r="J9">
         <v>2</v>
@@ -1767,8 +1957,10 @@
       <c r="P9">
         <v>30</v>
       </c>
-      <c r="Q9" t="s">
-        <v>57</v>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Smelts ore and produces furnace materials.</t>
+        </is>
       </c>
       <c r="R9">
         <v>1</v>
@@ -1780,12 +1972,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="B10">
         <v>30000006</v>
       </c>
-      <c r="C10" t="s">
-        <v>58</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1799,8 +1993,10 @@
       <c r="G10">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
-        <v>59</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Map/Buildings/Prefabs/WorldBlacksmith.prefab</t>
+        </is>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1823,8 +2019,10 @@
       <c r="P10">
         <v>40</v>
       </c>
-      <c r="Q10" t="s">
-        <v>60</v>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Processes metal and blacksmith recipes.</t>
+        </is>
       </c>
       <c r="R10">
         <v>1</v>
@@ -1836,12 +2034,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="B11">
         <v>30000007</v>
       </c>
-      <c r="C11" t="s">
-        <v>61</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mill</t>
+        </is>
       </c>
       <c r="D11">
         <v>7</v>
@@ -1855,8 +2055,10 @@
       <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11" t="s">
-        <v>62</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Map/Buildings/Prefabs/WorldMill.prefab</t>
+        </is>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1879,8 +2081,10 @@
       <c r="P11">
         <v>50</v>
       </c>
-      <c r="Q11" t="s">
-        <v>63</v>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Processes crops into food materials.</t>
+        </is>
       </c>
       <c r="R11">
         <v>1</v>
@@ -1892,12 +2096,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="B12">
         <v>30001001</v>
       </c>
-      <c r="C12" t="s">
-        <v>64</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Crop Field</t>
+        </is>
       </c>
       <c r="D12">
         <v>8</v>
@@ -1911,8 +2117,10 @@
       <c r="G12">
         <v>1</v>
       </c>
-      <c r="H12" t="s">
-        <v>65</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Map/Farming/Prefabs/WorldFarmPlot.prefab</t>
+        </is>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1935,8 +2143,10 @@
       <c r="P12">
         <v>10</v>
       </c>
-      <c r="Q12" t="s">
-        <v>66</v>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Field for crop planting and automatic crop output.</t>
+        </is>
       </c>
       <c r="R12">
         <v>1</v>
@@ -1948,12 +2158,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="B13">
         <v>30001002</v>
       </c>
-      <c r="C13" t="s">
-        <v>67</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Flower Field</t>
+        </is>
       </c>
       <c r="D13">
         <v>8</v>
@@ -1967,8 +2179,10 @@
       <c r="G13">
         <v>1</v>
       </c>
-      <c r="H13" t="s">
-        <v>65</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Map/Farming/Prefabs/WorldFarmPlot.prefab</t>
+        </is>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1991,8 +2205,10 @@
       <c r="P13">
         <v>20</v>
       </c>
-      <c r="Q13" t="s">
-        <v>68</v>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Field for flower planting and automatic flower output.</t>
+        </is>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2004,12 +2220,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="B14">
         <v>30001003</v>
       </c>
-      <c r="C14" t="s">
-        <v>69</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Herb Field</t>
+        </is>
       </c>
       <c r="D14">
         <v>8</v>
@@ -2023,8 +2241,10 @@
       <c r="G14">
         <v>1</v>
       </c>
-      <c r="H14" t="s">
-        <v>65</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Map/Farming/Prefabs/WorldFarmPlot.prefab</t>
+        </is>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2047,8 +2267,10 @@
       <c r="P14">
         <v>30</v>
       </c>
-      <c r="Q14" t="s">
-        <v>70</v>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Field for herb planting and automatic herb output.</t>
+        </is>
       </c>
       <c r="R14">
         <v>1</v>
@@ -2060,12 +2282,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="B15">
         <v>30002001</v>
       </c>
-      <c r="C15" t="s">
-        <v>71</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Stone Mine</t>
+        </is>
       </c>
       <c r="D15">
         <v>9</v>
@@ -2079,8 +2303,10 @@
       <c r="G15">
         <v>1</v>
       </c>
-      <c r="H15" t="s">
-        <v>72</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Structure/Stone/Meshy_AI_Stone_Pyramid_with_Gr_0629095812_texture.prefab</t>
+        </is>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2103,8 +2329,10 @@
       <c r="P15">
         <v>10</v>
       </c>
-      <c r="Q15" t="s">
-        <v>73</v>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Resource building for stone output.</t>
+        </is>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2116,12 +2344,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="B16">
         <v>30002002</v>
       </c>
-      <c r="C16" t="s">
-        <v>74</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Copper Mine</t>
+        </is>
       </c>
       <c r="D16">
         <v>9</v>
@@ -2135,8 +2365,10 @@
       <c r="G16">
         <v>1</v>
       </c>
-      <c r="H16" t="s">
-        <v>75</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Structure/Mine/Mine.prefab</t>
+        </is>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2159,8 +2391,10 @@
       <c r="P16">
         <v>20</v>
       </c>
-      <c r="Q16" t="s">
-        <v>76</v>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Resource building for copper ore output.</t>
+        </is>
       </c>
       <c r="R16">
         <v>1</v>
@@ -2172,12 +2406,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="B17">
         <v>30002003</v>
       </c>
-      <c r="C17" t="s">
-        <v>77</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Iron Mine</t>
+        </is>
       </c>
       <c r="D17">
         <v>9</v>
@@ -2191,8 +2427,10 @@
       <c r="G17">
         <v>1</v>
       </c>
-      <c r="H17" t="s">
-        <v>75</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Structure/Mine/Mine.prefab</t>
+        </is>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2215,8 +2453,10 @@
       <c r="P17">
         <v>30</v>
       </c>
-      <c r="Q17" t="s">
-        <v>78</v>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Resource building for iron ore output.</t>
+        </is>
       </c>
       <c r="R17">
         <v>1</v>
